--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/o-higgins.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1038"/>
+  <dimension ref="A1:M1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -46655,7 +46655,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>1732-7-CM26</t>
+          <t>1126920-159-CM26</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -46680,12 +46680,12 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>62.000.790-0</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE COLCHAGUA</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -46695,32 +46695,28 @@
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>LIBRERÍA FUTURO</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K723" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.402.891-0</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>878.22</v>
+        <v>9021.41</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>1126920-159-CM26</t>
+          <t>1732-7-CM26</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -46745,12 +46741,12 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>62.000.790-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE COLCHAGUA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -46760,22 +46756,26 @@
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>LIBRERÍA FUTURO</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>76.402.891-0</t>
-        </is>
-      </c>
-      <c r="K724" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>9021.41</v>
+        <v>878.22</v>
       </c>
     </row>
     <row r="725">
@@ -53871,7 +53871,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>3994-168-CM26</t>
+          <t>1499900-109-CM26</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -53896,12 +53896,12 @@
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H835" t="inlineStr">
@@ -53911,12 +53911,12 @@
       </c>
       <c r="I835" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J835" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K835" t="inlineStr">
@@ -53930,13 +53930,13 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>2643.71</v>
+        <v>1117.99</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>1499900-109-CM26</t>
+          <t>3994-168-CM26</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -53961,12 +53961,12 @@
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H836" t="inlineStr">
@@ -53976,12 +53976,12 @@
       </c>
       <c r="I836" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J836" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K836" t="inlineStr">
@@ -53995,7 +53995,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>1117.99</v>
+        <v>2643.71</v>
       </c>
     </row>
     <row r="837">
@@ -59758,7 +59758,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>3863-265-CM26</t>
+          <t>3863-264-CM26</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -59817,13 +59817,13 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>777.36</v>
+        <v>1016.09</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>3863-264-CM26</t>
+          <t>3863-265-CM26</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -59882,7 +59882,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>1016.09</v>
+        <v>777.36</v>
       </c>
     </row>
     <row r="928">
@@ -60213,7 +60213,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>642-146-CM26</t>
+          <t>1402-434-CM26</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -60238,12 +60238,12 @@
       </c>
       <c r="F933" t="inlineStr">
         <is>
-          <t>61.818.000-K</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H933" t="inlineStr">
@@ -60253,28 +60253,32 @@
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>MABEDUNA COMERCIAL LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J933" t="inlineStr">
         <is>
-          <t>77.211.666-7</t>
-        </is>
-      </c>
-      <c r="K933" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>861.34</v>
+        <v>2004.12</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>2675-342-CM26</t>
+          <t>642-146-CM26</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -60299,12 +60303,12 @@
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.818.000-K</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
         </is>
       </c>
       <c r="H934" t="inlineStr">
@@ -60314,32 +60318,28 @@
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MABEDUNA COMERCIAL LIMITADA</t>
         </is>
       </c>
       <c r="J934" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K934" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.211.666-7</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr"/>
       <c r="L934" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>1197.95</v>
+        <v>861.34</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>1402-434-CM26</t>
+          <t>1402-433-CM26</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -60379,17 +60379,17 @@
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J935" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K935" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L935" t="inlineStr">
@@ -60398,13 +60398,13 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>2004.12</v>
+        <v>874.5599999999999</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>1402-433-CM26</t>
+          <t>2675-342-CM26</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -60429,12 +60429,12 @@
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H936" t="inlineStr">
@@ -60463,7 +60463,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>874.5599999999999</v>
+        <v>1197.95</v>
       </c>
     </row>
     <row r="937">
@@ -61436,7 +61436,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>2205-121-CM26</t>
+          <t>2778-536-CM26</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -61456,17 +61456,17 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>61.602.143-5</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G952" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H952" t="inlineStr">
@@ -61476,28 +61476,32 @@
       </c>
       <c r="I952" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J952" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K952" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L952" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>1860.11</v>
+        <v>1158.42</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>2778-536-CM26</t>
+          <t>2205-121-CM26</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -61517,17 +61521,17 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.143-5</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H953" t="inlineStr">
@@ -61537,32 +61541,28 @@
       </c>
       <c r="I953" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J953" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K953" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.943.080-6</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr"/>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>1158.42</v>
+        <v>1860.11</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>3982-373-CM26</t>
+          <t>1623-382-CM26</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
@@ -61587,12 +61587,12 @@
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H954" t="inlineStr">
@@ -61621,13 +61621,13 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>2013.91</v>
+        <v>1352.04</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>1623-382-CM26</t>
+          <t>3982-373-CM26</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -61652,12 +61652,12 @@
       </c>
       <c r="F955" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G955" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H955" t="inlineStr">
@@ -61686,7 +61686,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>1352.04</v>
+        <v>2013.91</v>
       </c>
     </row>
     <row r="956">
@@ -61887,7 +61887,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>557639-1956-CM26</t>
+          <t>557639-1959-CM26</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -61927,32 +61927,28 @@
       </c>
       <c r="I959" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J959" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
-        </is>
-      </c>
-      <c r="K959" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr"/>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>2504.59</v>
+        <v>4725.04</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>557639-1959-CM26</t>
+          <t>557639-1956-CM26</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -61992,22 +61988,26 @@
       </c>
       <c r="I960" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J960" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K960" t="inlineStr"/>
+          <t>96.972.190-2</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L960" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>4725.04</v>
+        <v>2504.59</v>
       </c>
     </row>
     <row r="961">
@@ -62078,7 +62078,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>4737-142-CM26</t>
+          <t>1627-1187-CM26</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -62103,12 +62103,12 @@
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H962" t="inlineStr">
@@ -62118,12 +62118,12 @@
       </c>
       <c r="I962" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K962" t="inlineStr">
@@ -62137,13 +62137,13 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>1931.06</v>
+        <v>2094.88</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>1627-1185-CM26</t>
+          <t>4737-142-CM26</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -62168,12 +62168,12 @@
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H963" t="inlineStr">
@@ -62183,12 +62183,12 @@
       </c>
       <c r="I963" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K963" t="inlineStr">
@@ -62202,13 +62202,13 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>10927.82</v>
+        <v>1931.06</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>1627-1187-CM26</t>
+          <t>1627-1185-CM26</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -62248,12 +62248,12 @@
       </c>
       <c r="I964" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K964" t="inlineStr">
@@ -62267,13 +62267,13 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>2094.88</v>
+        <v>10927.82</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>1079563-383-CM26</t>
+          <t>3996-411-CM26</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -62293,17 +62293,17 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>61.978.680-7</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -62313,12 +62313,12 @@
       </c>
       <c r="I965" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K965" t="inlineStr">
@@ -62332,13 +62332,13 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>12109.1</v>
+        <v>1056.46</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>3996-411-CM26</t>
+          <t>1079563-383-CM26</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -62358,17 +62358,17 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>61.978.680-7</t>
         </is>
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
@@ -62378,12 +62378,12 @@
       </c>
       <c r="I966" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K966" t="inlineStr">
@@ -62397,13 +62397,13 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>1056.46</v>
+        <v>12109.1</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>4769-92-CM26</t>
+          <t>594965-149-CM26</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -62423,17 +62423,17 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>69.091.400-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -62462,13 +62462,13 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>778.6900000000001</v>
+        <v>1556.38</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>594965-149-CM26</t>
+          <t>1575-80-CM26</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -62488,17 +62488,17 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
@@ -62508,12 +62508,12 @@
       </c>
       <c r="I968" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K968" t="inlineStr">
@@ -62527,13 +62527,13 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>1556.38</v>
+        <v>13267.9</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>1575-80-CM26</t>
+          <t>1575-81-CM26</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -62553,7 +62553,7 @@
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
@@ -62592,13 +62592,13 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>13267.9</v>
+        <v>13465.54</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>1575-81-CM26</t>
+          <t>4769-92-CM26</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -62618,17 +62618,17 @@
       </c>
       <c r="E970" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.091.400-K</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
@@ -62638,12 +62638,12 @@
       </c>
       <c r="I970" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K970" t="inlineStr">
@@ -62657,7 +62657,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>13465.54</v>
+        <v>778.6900000000001</v>
       </c>
     </row>
     <row r="971">
@@ -62728,7 +62728,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>1622-1153-CM26</t>
+          <t>889473-1567-CM26</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -62753,12 +62753,12 @@
       </c>
       <c r="F972" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G972" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H972" t="inlineStr">
@@ -62768,12 +62768,12 @@
       </c>
       <c r="I972" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J972" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K972" t="inlineStr">
@@ -62787,13 +62787,13 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>950.99</v>
+        <v>3829.54</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>889473-1567-CM26</t>
+          <t>1622-1153-CM26</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -62818,12 +62818,12 @@
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
@@ -62833,12 +62833,12 @@
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K973" t="inlineStr">
@@ -62852,7 +62852,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>3829.54</v>
+        <v>950.99</v>
       </c>
     </row>
     <row r="974">
@@ -63370,7 +63370,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>1656-244-CM26</t>
+          <t>1656-238-CM26</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -63429,13 +63429,13 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>1840.36</v>
+        <v>933.26</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>1656-238-CM26</t>
+          <t>1656-244-CM26</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>933.26</v>
+        <v>1840.36</v>
       </c>
     </row>
     <row r="984">
@@ -63886,7 +63886,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>1699-120-CM26</t>
+          <t>557639-2423-CM26</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -63911,12 +63911,12 @@
       </c>
       <c r="F990" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H990" t="inlineStr">
@@ -63926,17 +63926,17 @@
       </c>
       <c r="I990" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J990" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K990" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L990" t="inlineStr">
@@ -63945,13 +63945,13 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>5062.72</v>
+        <v>1287.71</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>557639-2423-CM26</t>
+          <t>1699-120-CM26</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -63976,12 +63976,12 @@
       </c>
       <c r="F991" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G991" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H991" t="inlineStr">
@@ -63991,17 +63991,17 @@
       </c>
       <c r="I991" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J991" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K991" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L991" t="inlineStr">
@@ -64010,13 +64010,13 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>1287.71</v>
+        <v>5062.72</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>1501721-85-CM26</t>
+          <t>1501721-90-CM26</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -64056,17 +64056,17 @@
       </c>
       <c r="I992" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J992" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K992" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L992" t="inlineStr">
@@ -64075,13 +64075,13 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>5207.19</v>
+        <v>1147.75</v>
       </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>1699-121-CM26</t>
+          <t>1501721-85-CM26</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -64106,12 +64106,12 @@
       </c>
       <c r="F993" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G993" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H993" t="inlineStr">
@@ -64121,17 +64121,17 @@
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA INFINITO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
         <is>
-          <t>77.499.324-K</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L993" t="inlineStr">
@@ -64140,13 +64140,13 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>1389.97</v>
+        <v>5207.19</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>1699-122-CM26</t>
+          <t>1699-121-CM26</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -64186,12 +64186,12 @@
       </c>
       <c r="I994" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIALIZADORA INFINITO SPA</t>
         </is>
       </c>
       <c r="J994" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.499.324-K</t>
         </is>
       </c>
       <c r="K994" t="inlineStr">
@@ -64205,13 +64205,13 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>1736.69</v>
+        <v>1389.97</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>1501721-90-CM26</t>
+          <t>1699-122-CM26</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -64236,12 +64236,12 @@
       </c>
       <c r="F995" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H995" t="inlineStr">
@@ -64251,17 +64251,17 @@
       </c>
       <c r="I995" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J995" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K995" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L995" t="inlineStr">
@@ -64270,13 +64270,13 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>1147.75</v>
+        <v>1736.69</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>557639-2435-CM26</t>
+          <t>2568-172-CM26</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -64301,12 +64301,12 @@
       </c>
       <c r="F996" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G996" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H996" t="inlineStr">
@@ -64316,28 +64316,32 @@
       </c>
       <c r="I996" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J996" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K996" t="inlineStr"/>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L996" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>3595.77</v>
+        <v>1390.38</v>
       </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>3928-1263-CM26</t>
+          <t>557639-2435-CM26</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -64357,17 +64361,17 @@
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G997" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H997" t="inlineStr">
@@ -64377,32 +64381,28 @@
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J997" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K997" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr"/>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>757.49</v>
+        <v>3595.77</v>
       </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>557639-2545-CM26</t>
+          <t>3928-1263-CM26</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -64422,17 +64422,17 @@
       </c>
       <c r="E998" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G998" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H998" t="inlineStr">
@@ -64442,12 +64442,12 @@
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J998" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K998" t="inlineStr">
@@ -64461,13 +64461,13 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>4961.64</v>
+        <v>757.49</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>1622-1255-CM26</t>
+          <t>557639-2545-CM26</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -64487,17 +64487,17 @@
       </c>
       <c r="E999" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F999" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G999" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H999" t="inlineStr">
@@ -64507,12 +64507,12 @@
       </c>
       <c r="I999" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J999" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K999" t="inlineStr">
@@ -64526,13 +64526,13 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>847.87</v>
+        <v>4961.64</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>2778-601-CM26</t>
+          <t>1622-1255-CM26</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -64547,22 +64547,22 @@
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G1000" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H1000" t="inlineStr">
@@ -64572,12 +64572,12 @@
       </c>
       <c r="I1000" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1000" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1000" t="inlineStr">
@@ -64591,13 +64591,13 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>1508.25</v>
+        <v>847.87</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>1628-295-CM26</t>
+          <t>2778-601-CM26</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -64617,17 +64617,17 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
-          <t>61.602.132-k</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G1001" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H1001" t="inlineStr">
@@ -64637,12 +64637,12 @@
       </c>
       <c r="I1001" t="inlineStr">
         <is>
-          <t>COMERCIAL GMA SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J1001" t="inlineStr">
         <is>
-          <t>77.053.654-5</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K1001" t="inlineStr">
@@ -64656,13 +64656,13 @@
         </is>
       </c>
       <c r="M1001" s="2" t="n">
-        <v>1130.82</v>
+        <v>1508.25</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>2778-609-CM26</t>
+          <t>1628-295-CM26</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -64672,27 +64672,27 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.602.132-k</t>
         </is>
       </c>
       <c r="G1002" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE GRANEROS</t>
         </is>
       </c>
       <c r="H1002" t="inlineStr">
@@ -64702,12 +64702,12 @@
       </c>
       <c r="I1002" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL GMA SPA</t>
         </is>
       </c>
       <c r="J1002" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.053.654-5</t>
         </is>
       </c>
       <c r="K1002" t="inlineStr">
@@ -64721,13 +64721,13 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>1839.12</v>
+        <v>1130.82</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>552757-250-CM26</t>
+          <t>2778-609-CM26</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -64752,12 +64752,12 @@
       </c>
       <c r="F1003" t="inlineStr">
         <is>
-          <t>69.091.200-7</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G1003" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H1003" t="inlineStr">
@@ -64767,17 +64767,17 @@
       </c>
       <c r="I1003" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J1003" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1003" t="inlineStr">
@@ -64786,13 +64786,13 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>1231.87</v>
+        <v>1839.12</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>3864-299-CM26</t>
+          <t>552757-250-CM26</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -64807,7 +64807,7 @@
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
@@ -64817,12 +64817,12 @@
       </c>
       <c r="F1004" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.091.200-7</t>
         </is>
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H1004" t="inlineStr">
@@ -64832,17 +64832,17 @@
       </c>
       <c r="I1004" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1004" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1004" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1004" t="inlineStr">
@@ -64851,13 +64851,13 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>876.35</v>
+        <v>1231.87</v>
       </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>1256505-247-CM26</t>
+          <t>3864-299-CM26</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -64882,12 +64882,12 @@
       </c>
       <c r="F1005" t="inlineStr">
         <is>
-          <t>71.015.300-0</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H1005" t="inlineStr">
@@ -64897,17 +64897,17 @@
       </c>
       <c r="I1005" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J1005" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K1005" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L1005" t="inlineStr">
@@ -64916,13 +64916,13 @@
         </is>
       </c>
       <c r="M1005" s="2" t="n">
-        <v>1159.62</v>
+        <v>876.35</v>
       </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>3635-197-CM26</t>
+          <t>1256505-247-CM26</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -64947,12 +64947,12 @@
       </c>
       <c r="F1006" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>71.015.300-0</t>
         </is>
       </c>
       <c r="G1006" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H1006" t="inlineStr">
@@ -64962,17 +64962,17 @@
       </c>
       <c r="I1006" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J1006" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K1006" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1006" t="inlineStr">
@@ -64981,13 +64981,13 @@
         </is>
       </c>
       <c r="M1006" s="2" t="n">
-        <v>3266.65</v>
+        <v>1159.62</v>
       </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>3928-1293-CM26</t>
+          <t>3635-197-CM26</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -65002,22 +65002,22 @@
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
-          <t>69.091.201-5</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G1007" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H1007" t="inlineStr">
@@ -65027,17 +65027,17 @@
       </c>
       <c r="I1007" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1007" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1007" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1007" t="inlineStr">
@@ -65046,13 +65046,13 @@
         </is>
       </c>
       <c r="M1007" s="2" t="n">
-        <v>800.52</v>
+        <v>3266.65</v>
       </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>557639-2566-CM26</t>
+          <t>3928-1293-CM26</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
@@ -65067,22 +65067,22 @@
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>69.091.201-5</t>
         </is>
       </c>
       <c r="G1008" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H1008" t="inlineStr">
@@ -65092,28 +65092,32 @@
       </c>
       <c r="I1008" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J1008" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K1008" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1008" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1008" s="2" t="n">
-        <v>5053.31</v>
+        <v>800.52</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>557639-2565-CM26</t>
+          <t>557639-2566-CM26</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -65168,13 +65172,13 @@
         </is>
       </c>
       <c r="M1009" s="2" t="n">
-        <v>2071.12</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>1620-223-CM26</t>
+          <t>557639-2565-CM26</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
@@ -65189,22 +65193,22 @@
       </c>
       <c r="D1010" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G1010" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H1010" t="inlineStr">
@@ -65214,32 +65218,28 @@
       </c>
       <c r="I1010" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J1010" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K1010" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr"/>
       <c r="L1010" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1010" s="2" t="n">
-        <v>736.86</v>
+        <v>2071.12</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>3635-199-CM26</t>
+          <t>1620-223-CM26</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -65259,17 +65259,17 @@
       </c>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G1011" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H1011" t="inlineStr">
@@ -65279,17 +65279,17 @@
       </c>
       <c r="I1011" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1011" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
@@ -65298,13 +65298,13 @@
         </is>
       </c>
       <c r="M1011" s="2" t="n">
-        <v>774.89</v>
+        <v>736.86</v>
       </c>
     </row>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>3656-671-CM26</t>
+          <t>3635-199-CM26</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
@@ -65329,12 +65329,12 @@
       </c>
       <c r="F1012" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G1012" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H1012" t="inlineStr">
@@ -65344,17 +65344,17 @@
       </c>
       <c r="I1012" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J1012" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K1012" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L1012" t="inlineStr">
@@ -65363,13 +65363,13 @@
         </is>
       </c>
       <c r="M1012" s="2" t="n">
-        <v>908.84</v>
+        <v>774.89</v>
       </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>3635-200-CM26</t>
+          <t>3656-671-CM26</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -65384,7 +65384,7 @@
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
@@ -65394,12 +65394,12 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H1013" t="inlineStr">
@@ -65409,17 +65409,17 @@
       </c>
       <c r="I1013" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1013" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1013" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1013" t="inlineStr">
@@ -65428,13 +65428,13 @@
         </is>
       </c>
       <c r="M1013" s="2" t="n">
-        <v>2496.87</v>
+        <v>908.84</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>1213444-458-CM26</t>
+          <t>3635-200-CM26</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
@@ -65459,12 +65459,12 @@
       </c>
       <c r="F1014" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H1014" t="inlineStr">
@@ -65474,17 +65474,17 @@
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J1014" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L1014" t="inlineStr">
@@ -65493,13 +65493,13 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>1662.47</v>
+        <v>2496.87</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>2778-629-CM26</t>
+          <t>1213444-458-CM26</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -65524,12 +65524,12 @@
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>71.328.600-1</t>
         </is>
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
@@ -65539,17 +65539,17 @@
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J1015" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L1015" t="inlineStr">
@@ -65558,13 +65558,13 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>4002.39</v>
+        <v>1662.47</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>2778-630-CM26</t>
+          <t>2778-629-CM26</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -65623,13 +65623,13 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>2776.34</v>
+        <v>4002.39</v>
       </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>2778-631-CM26</t>
+          <t>2778-630-CM26</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -65688,13 +65688,13 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>1700.06</v>
+        <v>2776.34</v>
       </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>1402-591-CM26</t>
+          <t>2778-631-CM26</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
@@ -65714,17 +65714,17 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr">
@@ -65734,28 +65734,32 @@
       </c>
       <c r="I1018" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J1018" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
-        </is>
-      </c>
-      <c r="K1018" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1018" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1018" s="2" t="n">
-        <v>735.1</v>
+        <v>1700.06</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>3983-255-CM26</t>
+          <t>1402-591-CM26</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -65770,22 +65774,22 @@
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
@@ -65795,32 +65799,28 @@
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J1019" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
-        </is>
-      </c>
-      <c r="K1019" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+          <t>76.943.080-6</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr"/>
       <c r="L1019" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>2055.54</v>
+        <v>735.1</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>3283-58-CM26</t>
+          <t>3983-255-CM26</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -65840,17 +65840,17 @@
       </c>
       <c r="E1020" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
@@ -65860,17 +65860,17 @@
       </c>
       <c r="I1020" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J1020" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K1020" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L1020" t="inlineStr">
@@ -65879,13 +65879,13 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>2615.88</v>
+        <v>2055.54</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>1562-481-CM26</t>
+          <t>3283-58-CM26</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -65910,12 +65910,12 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
@@ -65925,28 +65925,32 @@
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1021" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K1021" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1021" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>853.71</v>
+        <v>2615.88</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>3635-201-CM26</t>
+          <t>1562-481-CM26</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -65966,17 +65970,17 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
@@ -65986,32 +65990,28 @@
       </c>
       <c r="I1022" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J1022" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K1022" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr"/>
       <c r="L1022" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>2025.3</v>
+        <v>853.71</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>2776-660-CM26</t>
+          <t>3635-201-CM26</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -66036,12 +66036,12 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
@@ -66051,17 +66051,17 @@
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1023" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1023" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1023" t="inlineStr">
@@ -66070,13 +66070,13 @@
         </is>
       </c>
       <c r="M1023" s="2" t="n">
-        <v>1089.49</v>
+        <v>2025.3</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>1529-273-CM26</t>
+          <t>2776-660-CM26</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -66091,7 +66091,7 @@
       </c>
       <c r="D1024" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E1024" t="inlineStr">
@@ -66101,12 +66101,12 @@
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
@@ -66135,13 +66135,13 @@
         </is>
       </c>
       <c r="M1024" s="2" t="n">
-        <v>758.22</v>
+        <v>1089.49</v>
       </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>3635-202-CM26</t>
+          <t>1529-273-CM26</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
@@ -66166,12 +66166,12 @@
       </c>
       <c r="F1025" t="inlineStr">
         <is>
-          <t>69.081.500-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G1025" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MALLOA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H1025" t="inlineStr">
@@ -66181,12 +66181,12 @@
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1025" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1025" t="inlineStr">
@@ -66200,13 +66200,13 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>3295.58</v>
+        <v>758.22</v>
       </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
         <is>
-          <t>3635-203-CM26</t>
+          <t>3635-202-CM26</t>
         </is>
       </c>
       <c r="B1026" t="inlineStr">
@@ -66246,17 +66246,17 @@
       </c>
       <c r="I1026" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J1026" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K1026" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1026" t="inlineStr">
@@ -66265,13 +66265,13 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>5736.19</v>
+        <v>3295.58</v>
       </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
         <is>
-          <t>3959-154-CM26</t>
+          <t>3635-203-CM26</t>
         </is>
       </c>
       <c r="B1027" t="inlineStr">
@@ -66286,7 +66286,7 @@
       </c>
       <c r="D1027" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E1027" t="inlineStr">
@@ -66296,12 +66296,12 @@
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t>69.073.800-7</t>
+          <t>69.081.500-1</t>
         </is>
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NAVIDAD</t>
+          <t>I MUNICIPALIDAD DE MALLOA</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
@@ -66311,17 +66311,17 @@
       </c>
       <c r="I1027" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J1027" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K1027" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L1027" t="inlineStr">
@@ -66330,13 +66330,13 @@
         </is>
       </c>
       <c r="M1027" s="2" t="n">
-        <v>1867.46</v>
+        <v>5736.19</v>
       </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
         <is>
-          <t>4738-293-CM26</t>
+          <t>3959-154-CM26</t>
         </is>
       </c>
       <c r="B1028" t="inlineStr">
@@ -66356,17 +66356,17 @@
       </c>
       <c r="E1028" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>69.073.800-7</t>
         </is>
       </c>
       <c r="G1028" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>I MUNICIPALIDAD DE NAVIDAD</t>
         </is>
       </c>
       <c r="H1028" t="inlineStr">
@@ -66395,13 +66395,13 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>853.8099999999999</v>
+        <v>1867.46</v>
       </c>
     </row>
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>2188-311-CM26</t>
+          <t>4738-293-CM26</t>
         </is>
       </c>
       <c r="B1029" t="inlineStr">
@@ -66421,17 +66421,17 @@
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t>61.602.134-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr">
@@ -66441,17 +66441,17 @@
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1029" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1029" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1029" t="inlineStr">
@@ -66460,13 +66460,13 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>1638.88</v>
+        <v>853.8099999999999</v>
       </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
         <is>
-          <t>1627-1342-CM26</t>
+          <t>2188-311-CM26</t>
         </is>
       </c>
       <c r="B1030" t="inlineStr">
@@ -66481,7 +66481,7 @@
       </c>
       <c r="D1030" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E1030" t="inlineStr">
@@ -66491,12 +66491,12 @@
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t>61.602.145-1</t>
+          <t>61.602.134-6</t>
         </is>
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
+          <t>SERVICIO DE SALUD HOSPITAL COINCO</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
@@ -66506,28 +66506,32 @@
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J1030" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
-        </is>
-      </c>
-      <c r="K1030" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1030" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1030" s="2" t="n">
-        <v>8491.57</v>
+        <v>1638.88</v>
       </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
         <is>
-          <t>2107-2256-CM26</t>
+          <t>1627-1342-CM26</t>
         </is>
       </c>
       <c r="B1031" t="inlineStr">
@@ -66552,12 +66556,12 @@
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.145-1</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN FERNANDO</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
@@ -66567,32 +66571,28 @@
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J1031" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K1031" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.957-3</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr"/>
       <c r="L1031" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>1876.12</v>
+        <v>8491.57</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
-          <t>3152-531-CM26</t>
+          <t>2107-2256-CM26</t>
         </is>
       </c>
       <c r="B1032" t="inlineStr">
@@ -66617,12 +66617,12 @@
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
@@ -66632,17 +66632,17 @@
       </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1032" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1032" t="inlineStr">
@@ -66651,13 +66651,13 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>1282.16</v>
+        <v>1876.12</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
         <is>
-          <t>2080-10605-CM26</t>
+          <t>3152-531-CM26</t>
         </is>
       </c>
       <c r="B1033" t="inlineStr">
@@ -66672,7 +66672,7 @@
       </c>
       <c r="D1033" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E1033" t="inlineStr">
@@ -66682,12 +66682,12 @@
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
@@ -66697,17 +66697,17 @@
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1033" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1033" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1033" t="inlineStr">
@@ -66716,13 +66716,13 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>4570.68</v>
+        <v>1282.16</v>
       </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>1626-222-CM26</t>
+          <t>2080-10605-CM26</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr">
@@ -66747,12 +66747,12 @@
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t>61.602.150-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G1034" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H1034" t="inlineStr">
@@ -66762,17 +66762,17 @@
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1034" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1034" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1034" t="inlineStr">
@@ -66781,13 +66781,13 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>1507.66</v>
+        <v>4570.68</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
         <is>
-          <t>1050283-542-CM26</t>
+          <t>1626-222-CM26</t>
         </is>
       </c>
       <c r="B1035" t="inlineStr">
@@ -66812,12 +66812,12 @@
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>61.602.150-8</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
@@ -66827,17 +66827,17 @@
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t>INVERSIÓN FUTURO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J1035" t="inlineStr">
         <is>
-          <t>78.094.613-K</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K1035" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L1035" t="inlineStr">
@@ -66846,13 +66846,13 @@
         </is>
       </c>
       <c r="M1035" s="2" t="n">
-        <v>1930.39</v>
+        <v>1507.66</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
         <is>
-          <t>1398-1369-CM26</t>
+          <t>1050283-542-CM26</t>
         </is>
       </c>
       <c r="B1036" t="inlineStr">
@@ -66877,12 +66877,12 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H1036" t="inlineStr">
@@ -66892,17 +66892,17 @@
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>INVERSIÓN FUTURO SPA</t>
         </is>
       </c>
       <c r="J1036" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.094.613-K</t>
         </is>
       </c>
       <c r="K1036" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="L1036" t="inlineStr">
@@ -66911,13 +66911,13 @@
         </is>
       </c>
       <c r="M1036" s="2" t="n">
-        <v>13290.29</v>
+        <v>1930.39</v>
       </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
         <is>
-          <t>2778-612-CM26</t>
+          <t>1398-1369-CM26</t>
         </is>
       </c>
       <c r="B1037" t="inlineStr">
@@ -66932,7 +66932,7 @@
       </c>
       <c r="D1037" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E1037" t="inlineStr">
@@ -66942,12 +66942,12 @@
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
@@ -66957,17 +66957,17 @@
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J1037" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K1037" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L1037" t="inlineStr">
@@ -66976,71 +66976,136 @@
         </is>
       </c>
       <c r="M1037" s="2" t="n">
-        <v>3382.35</v>
+        <v>13290.29</v>
       </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
+          <t>2778-612-CM26</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>69.081.200-2</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RENGO</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M1038" s="2" t="n">
+        <v>3382.35</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
           <t>2778-611-CM26</t>
         </is>
       </c>
-      <c r="B1038" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C1038" t="inlineStr">
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D1038" t="inlineStr">
+      <c r="D1039" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E1038" t="inlineStr">
+      <c r="E1039" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F1038" t="inlineStr">
+      <c r="F1039" t="inlineStr">
         <is>
           <t>69.081.200-2</t>
         </is>
       </c>
-      <c r="G1038" t="inlineStr">
+      <c r="G1039" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
-      <c r="H1038" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I1038" t="inlineStr">
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
-      <c r="J1038" t="inlineStr">
+      <c r="J1039" t="inlineStr">
         <is>
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K1038" t="inlineStr">
+      <c r="K1039" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L1038" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M1038" s="2" t="n">
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M1039" s="2" t="n">
         <v>3135.84</v>
       </c>
     </row>
